--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_51_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_51_R6.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.272</v>
+        <v>5.9022</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9575</v>
+        <v>5.3861</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3145</v>
+        <v>0.5161</v>
       </c>
       <c r="G2" t="n">
         <v>3.0761</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.054</v>
+        <v>-2.4238</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4936</v>
+        <v>-1.0651</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5604</v>
+        <v>-1.3587</v>
       </c>
       <c r="V2" t="n">
         <v>2.0026</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4381</v>
+        <v>4.3551</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9452</v>
+        <v>4.2991</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4929</v>
+        <v>0.056</v>
       </c>
       <c r="G3" t="n">
         <v>2.5661</v>
@@ -688,13 +688,13 @@
         <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6794</v>
+        <v>-1.7625</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3443</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3352</v>
+        <v>-0.7721</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7002</v>
+        <v>1.7571</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4973</v>
+        <v>2.2181</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7971</v>
+        <v>-0.461</v>
       </c>
       <c r="G4" t="n">
         <v>2.4912</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.005</v>
+        <v>-1.9481</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.3724</v>
+        <v>-1.0363</v>
       </c>
       <c r="V4" t="n">
         <v>1.214</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2165</v>
+        <v>0.2501</v>
       </c>
       <c r="E5" t="n">
         <v>0.0368</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1797</v>
+        <v>0.2133</v>
       </c>
       <c r="G5" t="n">
         <v>0.1941</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0131</v>
+        <v>-0.8535</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4945</v>
+        <v>-1.066</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4814</v>
+        <v>0.2125</v>
       </c>
       <c r="G6" t="n">
         <v>0.4533</v>
@@ -922,13 +922,13 @@
         <v>3.7112</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.6288</v>
+        <v>-2.4691</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7924</v>
+        <v>-1.3638</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8364</v>
+        <v>-1.1053</v>
       </c>
       <c r="V6" t="n">
         <v>0.9304</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.355</v>
+        <v>-1.5976</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2691</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0859</v>
+        <v>-0.8482</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2783</v>
+        <v>-0.8893</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9664</v>
+        <v>-1.5017</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2447</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7868000000000001</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8739</v>
+        <v>-0.1141</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0871</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0651</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0926</v>
+        <v>-1.3875</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1577</v>
+        <v>0.5756</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3809</v>
+        <v>-0.6025</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2636</v>
+        <v>-0.6721</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6445</v>
+        <v>0.0696</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.4975</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4975</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6985</v>
+        <v>-1.6513</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.6662</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.949</v>
+        <v>0.0149</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8893</v>
+        <v>-0.2783</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5017</v>
+        <v>0.9664</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6124000000000001</v>
+        <v>-1.2447</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1141</v>
+        <v>0.8739</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>-0.0871</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-1.0651</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3875</v>
+        <v>0.0926</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5756</v>
+        <v>-1.1577</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7033</v>
+        <v>-0.6772</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6721</v>
+        <v>-0.1336</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0312</v>
+        <v>-0.5436</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4975</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7385</v>
+        <v>-2.0849</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0075</v>
+        <v>-0.2717</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.746</v>
+        <v>-1.8132</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8635</v>
@@ -1156,13 +1156,13 @@
         <v>2.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4444</v>
+        <v>-1.7908</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3339</v>
+        <v>-0.613</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1105</v>
+        <v>-1.1778</v>
       </c>
       <c r="V9" t="n">
         <v>-1.214</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7088</v>
+        <v>-2.5909</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2463</v>
+        <v>-1.1283</v>
       </c>
       <c r="F10" t="n">
         <v>-1.4625</v>
@@ -1234,10 +1234,10 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6212</v>
+        <v>-0.5032</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U10" t="n">
         <v>-0.3224</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4057999999999984</v>
+        <v>-0.03239999999999865</v>
       </c>
       <c r="E12" t="n">
-        <v>3.582800000000001</v>
+        <v>3.956300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9886</v>
+        <v>-3.9887</v>
       </c>
       <c r="G12" t="n">
         <v>3.452500000000001</v>
@@ -1390,10 +1390,10 @@
         <v>19.7159</v>
       </c>
       <c r="S12" t="n">
-        <v>-12.8759</v>
+        <v>-12.5025</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.6027</v>
+        <v>-6.229299999999999</v>
       </c>
       <c r="U12" t="n">
         <v>-6.2732</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8366</v>
+        <v>4.0686</v>
       </c>
       <c r="E13" t="n">
-        <v>4.835</v>
+        <v>3.5375</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0016</v>
+        <v>0.5311</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4608</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4905</v>
+        <v>2.7226</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8036</v>
+        <v>1.5061</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6869</v>
+        <v>1.2164</v>
       </c>
       <c r="V13" t="n">
         <v>4.9667</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6933</v>
+        <v>3.7777</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3892</v>
+        <v>2.5071</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3042</v>
+        <v>1.2705</v>
       </c>
       <c r="G14" t="n">
         <v>1.6516</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5083</v>
+        <v>0.5926</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1336</v>
+        <v>-0.0156</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6418</v>
+        <v>0.6082</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3371</v>
+        <v>3.0157</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6913</v>
+        <v>2.4609</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3542</v>
+        <v>0.5548</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7528</v>
+        <v>1.894</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3961</v>
+        <v>-0.7058</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1489</v>
+        <v>2.5998</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0614</v>
+        <v>2.2446</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1443</v>
+        <v>-0.1478</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2057</v>
+        <v>2.3923</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3086</v>
+        <v>-0.3505</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2518</v>
+        <v>-0.5581</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0568</v>
+        <v>0.2075</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2801</v>
+        <v>0.8511</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9673</v>
+        <v>0.4483</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3128</v>
+        <v>0.4028</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>-0.4254</v>
       </c>
       <c r="W15" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7501</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0898</v>
+        <v>2.8419</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8712</v>
+        <v>3.9272</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2187</v>
+        <v>-1.0853</v>
       </c>
       <c r="G16" t="n">
-        <v>1.894</v>
+        <v>2.7528</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7058</v>
+        <v>-1.3961</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5998</v>
+        <v>4.1489</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2446</v>
+        <v>4.0614</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1478</v>
+        <v>-0.1443</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3923</v>
+        <v>4.2057</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3505</v>
+        <v>-1.3086</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5581</v>
+        <v>-1.2518</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2075</v>
+        <v>-0.0568</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0747</v>
+        <v>1.7849</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1415</v>
+        <v>1.2032</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0668</v>
+        <v>0.5816</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4254</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4254</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7635</v>
+        <v>-0.7548</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1161</v>
+        <v>-1.4685</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8796</v>
+        <v>0.7137</v>
       </c>
       <c r="G17" t="n">
-        <v>0.251</v>
+        <v>-0.1481</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6291</v>
+        <v>-0.312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8801</v>
+        <v>0.1639</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3592</v>
+        <v>0.4954</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1078</v>
+        <v>0.0672</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2514</v>
+        <v>0.4282</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1082</v>
+        <v>-0.6435</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7369</v>
+        <v>-0.3792</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3713</v>
+        <v>-0.2643</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.7834</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.7112</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2354</v>
+        <v>0.4138</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8625</v>
+        <v>-0.0156</v>
       </c>
       <c r="U17" t="n">
-        <v>0.373</v>
+        <v>0.4294</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4665</v>
+        <v>-0.7886</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3943</v>
+        <v>-0.7886</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9064</v>
+        <v>-0.8615</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5865</v>
+        <v>0.7962</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6801</v>
+        <v>-1.6577</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1481</v>
+        <v>-1.1727</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.312</v>
+        <v>-0.2292</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1639</v>
+        <v>-0.9435</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4954</v>
+        <v>0.45</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0672</v>
+        <v>0.3396</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4282</v>
+        <v>0.1104</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6435</v>
+        <v>-1.6227</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3792</v>
+        <v>-0.5688</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2643</v>
+        <v>-1.0539</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2623</v>
+        <v>0.7598</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1336</v>
+        <v>0.3462</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3958</v>
+        <v>0.4136</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7886</v>
+        <v>-1.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0981</v>
+        <v>-1.3208</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3244</v>
+        <v>0.1784</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4224</v>
+        <v>-1.4992</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1727</v>
+        <v>-0.8919</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2292</v>
+        <v>-1.1595</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9435</v>
+        <v>0.2677</v>
       </c>
       <c r="J19" t="n">
-        <v>0.45</v>
+        <v>0.1272</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3396</v>
+        <v>0.0168</v>
       </c>
       <c r="L19" t="n">
         <v>0.1104</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6227</v>
+        <v>-1.0191</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5688</v>
+        <v>-1.1763</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0539</v>
+        <v>0.1573</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5232</v>
+        <v>0.1072</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1256</v>
+        <v>0.0512</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6489</v>
+        <v>0.056</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4723</v>
+        <v>-1.8688</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0604</v>
+        <v>-1.5655</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5328</v>
+        <v>-0.3033</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8919</v>
+        <v>-2.9763</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1595</v>
+        <v>-2.1932</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2677</v>
+        <v>-0.7831</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1272</v>
+        <v>-1.6357</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0168</v>
+        <v>-1.4348</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1104</v>
+        <v>-0.201</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0191</v>
+        <v>-1.3405</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1763</v>
+        <v>-0.7584</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1573</v>
+        <v>-0.5821</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0444</v>
+        <v>0.6616</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0668</v>
+        <v>0.016</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0224</v>
+        <v>0.6456</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X20" t="n">
         <v>-0.5361</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8954</v>
+        <v>-2.0616</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1552</v>
+        <v>-1.4173</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7402</v>
+        <v>-0.6444</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9763</v>
+        <v>0.251</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1932</v>
+        <v>-0.6291</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7831</v>
+        <v>0.8801</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6357</v>
+        <v>1.3592</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4348</v>
+        <v>0.1078</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.201</v>
+        <v>1.2514</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3405</v>
+        <v>-1.1082</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7584</v>
+        <v>-0.7369</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5821</v>
+        <v>-0.3713</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.232</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R21" t="n">
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3651</v>
+        <v>1.9373</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5737</v>
+        <v>1.3291</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2087</v>
+        <v>0.6082</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6778999999999999</v>
+        <v>-1.4665</v>
       </c>
       <c r="W21" t="n">
-        <v>1.214</v>
+        <v>-0.3943</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1094</v>
+        <v>-2.9413</v>
       </c>
       <c r="E22" t="n">
         <v>-2.1874</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.922</v>
+        <v>-0.7539</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5626</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.7088</v>
       </c>
       <c r="T22" t="n">
         <v>0.3699</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1709</v>
+        <v>0.3389</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3061</v>
+        <v>-3.4893</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3699</v>
+        <v>-2.7801</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0638</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7895</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5194</v>
+        <v>2.3362</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4446</v>
+        <v>1.0343</v>
       </c>
       <c r="U23" t="n">
-        <v>2.0748</v>
+        <v>1.3019</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3247</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4055999999999997</v>
+        <v>0.4057999999999993</v>
       </c>
       <c r="E24" t="n">
-        <v>3.988599999999999</v>
+        <v>3.988499999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5828</v>
+        <v>-3.5829</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4525</v>
@@ -2317,7 +2317,7 @@
         <v>-2.9268</v>
       </c>
       <c r="P24" t="n">
-        <v>-8.118400000000001</v>
+        <v>-8.118399999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-19.7161</v>
@@ -2326,22 +2326,22 @@
         <v>11.5976</v>
       </c>
       <c r="S24" t="n">
-        <v>12.8758</v>
+        <v>12.8759</v>
       </c>
       <c r="T24" t="n">
         <v>6.2731</v>
       </c>
       <c r="U24" t="n">
-        <v>6.6028</v>
+        <v>6.6026</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8992999999999995</v>
+        <v>-0.8992999999999998</v>
       </c>
       <c r="W24" t="n">
-        <v>7.1733</v>
+        <v>7.173299999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.0726</v>
+        <v>-8.072600000000001</v>
       </c>
     </row>
   </sheetData>
